--- a/daily_matches/job_matches_2026-05-26.xlsx
+++ b/daily_matches/job_matches_2026-05-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI-Native Builder</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>TeraWatt Infrastructure</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.9</v>
+        <v>17.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Gemini, Copilot, Pinecone, Glue, MLflow, FastAPI, Docker, Kubernetes</t>
+          <t>RAG, Data Lake, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Databricks, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5397e30a285245d</t>
+          <t>https://www.indeed.com/viewjob?jk=ab18efde0a1dd056</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI Native Developer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.9</v>
+        <v>15.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Gemini, Copilot, Pinecone, Glue, MLflow, FastAPI, Docker, Kubernetes</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, Python</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbc661e109c14228</t>
+          <t>https://www.indeed.com/viewjob?jk=9f80cce2b9ebf257</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI-Native Builder</t>
+          <t>Senior Software Engineer, Data Platform (Canada)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.9</v>
+        <v>13.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Gemini, Copilot, Pinecone, Glue, MLflow, FastAPI, Docker, Kubernetes</t>
+          <t>Data Scientist, RAG, BigQuery, Docker, Kubernetes, Terraform, BigQuery, Kafka, Python, SQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37bc77d9dc22a6a9</t>
+          <t>https://www.indeed.com/viewjob?jk=4ddbaba31adfd57a</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI Native Developer</t>
+          <t>Engineer II – Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.9</v>
+        <v>10</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Gemini, Copilot, Pinecone, Glue, MLflow, FastAPI, Docker, Kubernetes</t>
+          <t>RAG, Copilot, Apache Airflow, Git, Snowflake, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba608063466f07bd</t>
+          <t>https://www.indeed.com/viewjob?jk=3de4614253463977</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AI Native Developer</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.9</v>
+        <v>10</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Gemini, Copilot, Pinecone, Glue, MLflow, FastAPI, Docker, Kubernetes</t>
+          <t>RAG, Docker, Kubernetes, PostgreSQL, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36ab7b1b575050e1</t>
+          <t>https://www.indeed.com/viewjob?jk=a043281f58642aa7</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AI-Native Builder</t>
+          <t>Customer Delivery Engineer, NASA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.9</v>
+        <v>10</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Gemini, Copilot, Pinecone, Glue, MLflow, FastAPI, Docker, Kubernetes</t>
+          <t>Copilot, Docker, Kubernetes, PostgreSQL, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,217 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc95b3c395886fe7</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>AI - Native Builder</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Newpage Digital Healthcare solutions</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, Gemini, Copilot, Pinecone, Glue, MLflow, Docker, Kubernetes, CI/CD</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bcd329279eb0cbc5</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>AI - Native Builder</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Newpage Digital Healthcare solutions</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, Gemini, Copilot, Pinecone, Glue, MLflow, Docker, Kubernetes, CI/CD</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0a8ea8730e4cf117</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>AI - Native Builder</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Newpage Digital Healthcare solutions</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, Gemini, Copilot, Pinecone, Glue, MLflow, Docker, Kubernetes, CI/CD</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c0214499e127c894</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>AI - Native Builder</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Newpage Digital Healthcare solutions</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, Gemini, Copilot, Pinecone, Glue, MLflow, Docker, Kubernetes, CI/CD</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3ad88277e472de1e</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Looking for a Senior Full Stack Developer</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>softai</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>LangChain, RAG, FastAPI, Docker, Kubernetes, CI/CD, PostgreSQL, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ed0a2a699b9900bb</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Generative AI Engineer</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>DATAIKU</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Gemini, Copilot, Prompt Engineering, Git, Python, R</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bdabd295d64bfe4e</t>
+          <t>https://www.indeed.com/viewjob?jk=b65162d89489ddd4</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-05-26.xlsx
+++ b/daily_matches/job_matches_2026-05-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,12 +468,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Software Engineer (Generalist)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>TeraWatt Infrastructure</t>
+          <t>Traba</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -482,11 +482,11 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.8</v>
+        <v>12.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Databricks, Kafka, PostgreSQL</t>
+          <t>RAG, Docker, GitHub Actions, Git, Kafka, PostgreSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab18efde0a1dd056</t>
+          <t>https://www.indeed.com/viewjob?jk=51f1171a53b3af1e</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Senior Software Engineer (Generalist)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Traba</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, Python</t>
+          <t>RAG, Docker, GitHub Actions, Git, Kafka, PostgreSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,19 +531,19 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f80cce2b9ebf257</t>
+          <t>https://www.indeed.com/viewjob?jk=e60680c4eaf60eb4</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Platform (Canada)</t>
+          <t>Full Stack Engineering Specialist - Freelance AI Trainer Project</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -552,38 +552,38 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, BigQuery, Docker, Kubernetes, Terraform, BigQuery, Kafka, Python, SQL</t>
+          <t>Docker, Kubernetes, CI/CD, NoSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ddbaba31adfd57a</t>
+          <t>https://www.indeed.com/viewjob?jk=8cb0ef8f3622c959</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Engineer II – Data Engineer</t>
+          <t>Software Engineer (Generalist)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Traba</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Apache Airflow, Git, Snowflake, Python, SQL, R, Scala</t>
+          <t>RAG, Docker, CI/CD, GitHub Actions, Git, PostgreSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,77 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3de4614253463977</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Solutions Architect</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>10</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, PostgreSQL, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a043281f58642aa7</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Customer Delivery Engineer, NASA</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>10</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Copilot, Docker, Kubernetes, PostgreSQL, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b65162d89489ddd4</t>
+          <t>https://www.indeed.com/viewjob?jk=fe77a9cad4a7eb54</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-05-26.xlsx
+++ b/daily_matches/job_matches_2026-05-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,12 +468,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Generalist)</t>
+          <t>Sr Field Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Traba</t>
+          <t>Striim</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -482,46 +482,46 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Docker, GitHub Actions, Git, Kafka, PostgreSQL, Python, SQL, R, Java</t>
+          <t>RAG, BigQuery, Kubernetes, Git, Snowflake, Databricks, BigQuery, Kafka, MySQL, Python</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51f1171a53b3af1e</t>
+          <t>https://www.indeed.com/viewjob?jk=960f767365c3fdc0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Generalist)</t>
+          <t>Senior Software Engineer, Backend</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Traba</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Torrance, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Docker, GitHub Actions, Git, Kafka, PostgreSQL, Python, SQL, R, Java</t>
+          <t>RAG, S3, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, R</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e60680c4eaf60eb4</t>
+          <t>https://www.indeed.com/viewjob?jk=36b655d5786f6e9c</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Full Stack Engineering Specialist - Freelance AI Trainer Project</t>
+          <t>AI Skill Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>QuadCode</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, NoSQL, Python, SQL, R, Java, Scala</t>
+          <t>LangChain, RAG, LLaMA, Gemini, Hugging Face, Pinecone, Prompt Engineering, Python, R, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,42 +566,182 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cb0ef8f3622c959</t>
+          <t>https://www.indeed.com/viewjob?jk=ac2e44ae619d94b0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer (Generalist)</t>
+          <t>Senior AI Scientist</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Traba</t>
+          <t>IQVIA</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, Databricks, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=81cfde54cbcb86b4</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>AI Developer</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>CLANDICA</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, Git, NoSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9e5ebcf762ccf83c</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer – Backend</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Finalcover LLC</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Arlington, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>S3, EC2, Docker, Kubernetes, Terraform, NoSQL, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=254d43c61e4dbbb4</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer - AI &amp; Credit Analytics</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Experian</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
         <v>10</v>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>RAG, Docker, CI/CD, GitHub Actions, Git, PostgreSQL, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fe77a9cad4a7eb54</t>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, CI/CD, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7ff0ff8ba451a61b</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Software Engineer - AI &amp; Cloud Engineering (Early to Mid Career, WI Based)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Flexcompute Inc.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Madison, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>10</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, Git, Python, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=226c65461c9c6f1a</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-05-26.xlsx
+++ b/daily_matches/job_matches_2026-05-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sr Field Engineer</t>
+          <t>Sr AI/ML Engineer, Cloud &amp; AI Solutions - Remote or Hybrid in MN or DC</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Striim</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>15.6</v>
+        <v>23.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Kubernetes, Git, Snowflake, Databricks, BigQuery, Kafka, MySQL, Python</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Hugging Face, FAISS, Pinecone, Prompt Engineering, TensorFlow</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,67 +496,67 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=960f767365c3fdc0</t>
+          <t>https://www.indeed.com/viewjob?jk=335ea2d7840c2301</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Backend</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Torrance, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14.4</v>
+        <v>18.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, S3, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, R</t>
+          <t>Machine Learning Engineer, LangChain, RAG, FAISS, Pinecone, ChromaDB, Prompt Engineering, TensorFlow, PyTorch, FastAPI</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36b655d5786f6e9c</t>
+          <t>https://www.indeed.com/viewjob?jk=7a38d25104c7179d</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI Skill Engineer</t>
+          <t>Senior Data Engineer, Platform Data</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>QuadCode</t>
+          <t>Leadfeeder</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>12.2</v>
+        <v>18.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Gemini, Hugging Face, Pinecone, Prompt Engineering, Python, R, Scala</t>
+          <t>RAG, S3, Athena, Redshift, BigQuery, Kinesis, CI/CD, Terraform, Snowflake, Databricks</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,67 +566,67 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac2e44ae619d94b0</t>
+          <t>https://www.indeed.com/viewjob?jk=d2b659aa81b3c306</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior AI Scientist</t>
+          <t>AI Solution Architect</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>IQVIA</t>
+          <t>Origence</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12.2</v>
+        <v>17.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, Databricks, Python, R, Scala</t>
+          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, Synapse, PostgreSQL, MySQL, MongoDB, NoSQL, Power BI</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81cfde54cbcb86b4</t>
+          <t>https://www.indeed.com/viewjob?jk=7e8da60d668640f5</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AI Developer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CLANDICA</t>
+          <t>Verizon</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.2</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, Git, NoSQL, Python, SQL, R, Scala</t>
+          <t>Data Scientist, RAG, Hugging Face, PyTorch, BigQuery, Docker, CI/CD, Git, Snowflake, BigQuery</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e5ebcf762ccf83c</t>
+          <t>https://www.indeed.com/viewjob?jk=661cb3c40e06d852</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – Backend</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Finalcover LLC</t>
+          <t>Macmillan Publishers</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>S3, EC2, Docker, Kubernetes, Terraform, NoSQL, SQL, R, Scala, Optimization</t>
+          <t>AI Engineer, RAG, BigQuery, CI/CD, GitHub Actions, Terraform, Git, Snowflake, BigQuery, PostgreSQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=254d43c61e4dbbb4</t>
+          <t>https://www.indeed.com/viewjob?jk=4eb1d2668d2c3bb3</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior AI Engineer - AI &amp; Credit Analytics</t>
+          <t>Senior Software Engineer, Data</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Experian</t>
+          <t>Lila Sciences</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>15.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, CI/CD, Python, SQL, R, Scala, Optimization</t>
+          <t>Machine Learning Engineer, RAG, PyTorch, FastAPI, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, NoSQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,42 +706,637 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ff0ff8ba451a61b</t>
+          <t>https://www.indeed.com/viewjob?jk=b975973860fe466c</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineer - AI &amp; Cloud Engineering (Early to Mid Career, WI Based)</t>
+          <t>Senior Software Engineer, Data</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Flexcompute Inc.</t>
+          <t>Lila Sciences</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, RAG, PyTorch, FastAPI, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, NoSQL</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b47adc71ffc989c2</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Site Reliability Engineer II (Remote, US)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Openly</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>RAG, BigQuery, Kubernetes, CI/CD, Terraform, Git, BigQuery, Kafka, PostgreSQL, Python</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c4c0d71f6d3e3d52</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Recutify Inc.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Prompt Engineering, Docker, Kubernetes, CI/CD, Databricks, Python</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2ee880f838d01800</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Senior Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Fustis LLC</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>El Paso, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Copilot, Cortex, Synapse, Data Lake, Git, Snowflake, Databricks, Power BI, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2e887fffa7d23b98</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>SEI Investments</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Oaks, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, AKS, Jenkins, Git, Snowflake, MySQL, MongoDB, SQL</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f9baacd75cf6077b</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Sr. Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Origence</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Irvine, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, Prompt Engineering, Cortex, Docker, Kubernetes, CI/CD, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0ce5b2d538a79f01</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>AI Engineering Coach</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Optwise Consulting</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, Git, Python</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d2e0bca8db6cf9af</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>GenAI Engineer</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Recutify Inc.</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Jenkins, Python, R</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2202143b81385abf</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Senior Backend Engineer</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Blitzy</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Cambridge, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Jenkins, Terraform, Git, MongoDB, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1e3cdb6215454b36</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Allruva Technology Services</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Data Scientist, TensorFlow, PyTorch, Hadoop, Tableau, Power BI, Python, SQL, R, Hypothesis Testing</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=678799d3acc28de9</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Growth</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Klaviyo</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>EC2, Terraform, Git, MySQL, Cassandra, Python, SQL, R, Java, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c49c39d5397a8a1b</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Sr Microsoft Purview Engineer</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Evolver Inc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, Copilot, Snowflake, Databricks, Power BI, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=50147c2ee6e1512f</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Applied AI Engineer</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>C&amp;W Services</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Cincinnati, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
         <v>10</v>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, Git, Python, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-05-26</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=226c65461c9c6f1a</t>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, MLflow, CI/CD, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ff7610eec0a5fdf4</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>AI Engineer Intern - USA</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Black Box</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>10</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, FastAPI, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a1a4c8f89e123124</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>AI Engineer Intern - USA</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Black Box</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>10</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, FastAPI, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=09c6e8eaa04b62d9</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Senior Data Analyst, Finance</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Equifax</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>St. Louis, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>BigQuery, Dataflow, BigQuery, Tableau, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b8e4e30c6d85ec39</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Sr. Engineer - Java Developer</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Genpact</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>10</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, Git, Kafka, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d76ff20c6f9e7a00</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>AWS Devops Engineer-100% Onsite</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>10</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>S3, EC2, Docker, Kubernetes, CI/CD, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=39d3550421b8adcd</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-05-26.xlsx
+++ b/daily_matches/job_matches_2026-05-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sr AI/ML Engineer, Cloud &amp; AI Solutions - Remote or Hybrid in MN or DC</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Klaxon Technolgies</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>23.3</v>
+        <v>38.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Hugging Face, FAISS, Pinecone, Prompt Engineering, TensorFlow</t>
+          <t>Data Scientist, RAG, Copilot, S3, Glue, Athena, Redshift, BigQuery, Synapse, Data Lake</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,24 +496,24 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=335ea2d7840c2301</t>
+          <t>https://www.indeed.com/viewjob?jk=3265598d80fd8a76</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Nexstar Media Group, Inc.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, LangChain, RAG, FAISS, Pinecone, ChromaDB, Prompt Engineering, TensorFlow, PyTorch, FastAPI</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, XGBoost, S3, EC2</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a38d25104c7179d</t>
+          <t>https://www.indeed.com/viewjob?jk=7b532541851ceb06</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Platform Data</t>
+          <t>Controllers, Software Engineering, Salt Lake City, Associate</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Leadfeeder</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, S3, Athena, Redshift, BigQuery, Kinesis, CI/CD, Terraform, Snowflake, Databricks</t>
+          <t>RAG, Copilot, Prompt Engineering, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,67 +566,67 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2b659aa81b3c306</t>
+          <t>https://www.indeed.com/viewjob?jk=81361a25f18bfa9e</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI Solution Architect</t>
+          <t>Agentic AI Developer Intern</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Origence</t>
+          <t>JobTarget</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.8</v>
+        <v>18.9</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, Synapse, PostgreSQL, MySQL, MongoDB, NoSQL, Power BI</t>
+          <t>AI Engineer, Generative AI, LangChain, LLaMA, Gemini, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e8da60d668640f5</t>
+          <t>https://www.indeed.com/viewjob?jk=a19ee90d5445904d</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Senior Engineer 2: AI Agentic Solutions (Hybrid - Seattle, WA)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Verizon</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>17.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Hugging Face, PyTorch, BigQuery, Docker, CI/CD, Git, Snowflake, BigQuery</t>
+          <t>RAG, Prompt Engineering, Redshift, BigQuery, Docker, Kubernetes, CI/CD, Git, BigQuery, Redshift</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=661cb3c40e06d852</t>
+          <t>https://www.indeed.com/viewjob?jk=d1942d9ec58e935c</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>AI Engineer / AI Analyst</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Macmillan Publishers</t>
+          <t>Light &amp; Wonder</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, BigQuery, CI/CD, GitHub Actions, Terraform, Git, Snowflake, BigQuery, PostgreSQL</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Copilot, Prompt Engineering, Docker, CI/CD</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4eb1d2668d2c3bb3</t>
+          <t>https://www.indeed.com/viewjob?jk=40e78b905dfc2ab3</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Lila Sciences</t>
+          <t>Prime Cargo People Logistics</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, PyTorch, FastAPI, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, NoSQL</t>
+          <t>S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b975973860fe466c</t>
+          <t>https://www.indeed.com/viewjob?jk=c504b34cabd6342d</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data</t>
+          <t>Applied AI Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Lila Sciences</t>
+          <t>SOCOTEC Group</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, PyTorch, FastAPI, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, NoSQL</t>
+          <t>AI Engineer, Data Scientist, LangChain, RAG, Hugging Face, TensorFlow, PyTorch, Docker, Git, Python</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b47adc71ffc989c2</t>
+          <t>https://www.indeed.com/viewjob?jk=7f5bc665ed4da059</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer II (Remote, US)</t>
+          <t>Senior Software Engineer, App</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Openly</t>
+          <t>Lila Sciences</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Kubernetes, CI/CD, Terraform, Git, BigQuery, Kafka, PostgreSQL, Python</t>
+          <t>AI Engineer, RAG, PyTorch, FastAPI, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, NoSQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4c0d71f6d3e3d52</t>
+          <t>https://www.indeed.com/viewjob?jk=ca392fa39b84631e</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior Software Engineer, App</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>Lila Sciences</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Prompt Engineering, Docker, Kubernetes, CI/CD, Databricks, Python</t>
+          <t>AI Engineer, RAG, PyTorch, FastAPI, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, NoSQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ee880f838d01800</t>
+          <t>https://www.indeed.com/viewjob?jk=f024bf694f893ebe</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Fustis LLC</t>
+          <t>Kohl's</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>El Paso, TX, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Copilot, Cortex, Synapse, Data Lake, Git, Snowflake, Databricks, Power BI, Python, SQL</t>
+          <t>RAG, Redshift, BigQuery, CI/CD, Snowflake, BigQuery, Redshift, Kafka, Python, SQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e887fffa7d23b98</t>
+          <t>https://www.indeed.com/viewjob?jk=877d45e3d1a625d6</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>DevOps Engineer I</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SEI Investments</t>
+          <t>Altanovo</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Oaks, PA, US USA</t>
+          <t>Vista, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, AKS, Jenkins, Git, Snowflake, MySQL, MongoDB, SQL</t>
+          <t>Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,67 +881,67 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9baacd75cf6077b</t>
+          <t>https://www.indeed.com/viewjob?jk=12280c742eb2756f</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sr. Platform Engineer</t>
+          <t>Full Stack AI + Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Origence</t>
+          <t>Techtorch</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Prompt Engineering, Cortex, Docker, Kubernetes, CI/CD, Terraform, Git</t>
+          <t>AI Engineer, RAG, MLflow, FastAPI, CI/CD, GitHub Actions, Git, Kafka, PostgreSQL, Python</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ce5b2d538a79f01</t>
+          <t>https://www.indeed.com/viewjob?jk=6740052e5af1c2fe</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AI Engineering Coach</t>
+          <t>Software Engineer III, Voice AI</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Optwise Consulting</t>
+          <t>Natera</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AI Engineer, Machine Learning Engineer, RAG, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, Git, Python</t>
+          <t>RAG, Prompt Engineering, S3, Docker, CI/CD, Git, Kafka, MySQL, NoSQL, SQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2e0bca8db6cf9af</t>
+          <t>https://www.indeed.com/viewjob?jk=2ff57ba86e213734</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>GenAI Engineer</t>
+          <t>Software Engineer, I - Data Engineering</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>TORC Robotics</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Jenkins, Python, R</t>
+          <t>RAG, Glue, Athena, Data Lake, Docker, Terraform, Databricks, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2202143b81385abf</t>
+          <t>https://www.indeed.com/viewjob?jk=196506204c7c944f</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Senior Forward Deployed Engineer - QuantumBlack, AI by McKinsey</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Blitzy</t>
+          <t>McKinsey &amp; Company</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Jenkins, Terraform, Git, MongoDB, NoSQL, Python, SQL, R</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e3cdb6215454b36</t>
+          <t>https://www.indeed.com/viewjob?jk=99421b7cddeacb9e</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Engineer, Backend Platform</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Allruva Technology Services</t>
+          <t>SpotHero</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Data Scientist, TensorFlow, PyTorch, Hadoop, Tableau, Power BI, Python, SQL, R, Hypothesis Testing</t>
+          <t>RAG, S3, EC2, Redshift, Kubernetes, Terraform, Git, Redshift, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=678799d3acc28de9</t>
+          <t>https://www.indeed.com/viewjob?jk=8abf869646b478a8</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Engineer II - Growth</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Klaviyo</t>
+          <t>Bamboo Health</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>EC2, Terraform, Git, MySQL, Cassandra, Python, SQL, R, Java, A/B Testing</t>
+          <t>RAG, Copilot, Redshift, Git, Redshift, PostgreSQL, MySQL, Tableau, Python, SQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c49c39d5397a8a1b</t>
+          <t>https://www.indeed.com/viewjob?jk=c11286aa0fcd0743</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr Microsoft Purview Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Evolver Inc</t>
+          <t>Kinsale Management Inc</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Copilot, Snowflake, Databricks, Power BI, R, Scala, Optimization</t>
+          <t>Generative AI, RAG, Copilot, Git, Snowflake, Databricks, PostgreSQL, MongoDB, SQL, R</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50147c2ee6e1512f</t>
+          <t>https://www.indeed.com/viewjob?jk=a938739108dd1870</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Applied AI Engineer</t>
+          <t>Senior Google Data (AI) Architect</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>C&amp;W Services</t>
+          <t>Huntington Bank</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, MLflow, CI/CD, Databricks, Python, SQL, R</t>
+          <t>RAG, Gemini, BigQuery, Dataflow, CI/CD, Terraform, BigQuery, Python, SQL, R</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff7610eec0a5fdf4</t>
+          <t>https://www.indeed.com/viewjob?jk=22c4098e5ff1d020</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AI Engineer Intern - USA</t>
+          <t>Software Engineer II - Java/Python</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Black Box</t>
+          <t>Bank of America</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, FastAPI, Python, R, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, MongoDB, Cassandra, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1a4c8f89e123124</t>
+          <t>https://www.indeed.com/viewjob?jk=e901ac4878117ce6</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AI Engineer Intern - USA</t>
+          <t>Sr. Software Engineer - Partnerships New Verticals (Remote)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Black Box</t>
+          <t>Rula</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, FastAPI, Python, R, Scala</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, PostgreSQL, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,67 +1231,67 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09c6e8eaa04b62d9</t>
+          <t>https://www.indeed.com/viewjob?jk=8eab594acdb8b152</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Analyst, Finance</t>
+          <t>Software Engineer, New College Grad - 2026, Austin</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>BigQuery, Dataflow, BigQuery, Tableau, Power BI, Python, SQL, R, Scala</t>
+          <t>LLaMA, Gemini, Copilot, Prompt Engineering, Git, MySQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8e4e30c6d85ec39</t>
+          <t>https://www.indeed.com/viewjob?jk=ceb35ab4e48f9daf</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sr. Engineer - Java Developer</t>
+          <t>Quantitative Analyst, Applied Biomechanics</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Genpact</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, Git, Kafka, SQL, R, Java, Scala, Optimization</t>
+          <t>RAG, BigQuery, MLflow, Docker, Git, BigQuery, MySQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,42 +1301,392 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d76ff20c6f9e7a00</t>
+          <t>https://www.indeed.com/viewjob?jk=258af574d127fcb7</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AWS Devops Engineer-100% Onsite</t>
+          <t>Quantitative Analyst, Applied Biomechanics</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Clearwater, FL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>RAG, BigQuery, MLflow, Docker, Git, BigQuery, MySQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1f1d68d8e7ca1180</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Engineer/Sr Engineer, IT Software</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>American Airlines</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Fort Worth, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>FastAPI, Docker, Kubernetes, GitHub Actions, Git, Kafka, PostgreSQL, MongoDB, SQL, R</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e70cddc4d406c6fc</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Foster City, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Generative AI, Jenkins, Git, MySQL, NoSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=efbb1200b91a59c6</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Senior Engineer</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Presidio</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Git, MySQL, MongoDB, Cassandra, NoSQL, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=496912407ad371bf</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Eden Prairie, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, Git, Kafka, PostgreSQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4af07293980f51d9</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Senior Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Order.co</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Manhattan, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
         <v>10</v>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>S3, EC2, Docker, Kubernetes, CI/CD, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=39d3550421b8adcd</t>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=26dc08400f4a2c87</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Senior Full-Stack AI Engineer (Web + iOS)</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>TWG Global AI</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Santa Monica, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>10</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, RAG, CI/CD, PostgreSQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8ff6466b258b4c3d</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Senior Full-Stack AI Engineer (Web + iOS)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>TWG Global AI</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>10</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, RAG, CI/CD, PostgreSQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dec95a69baa7e315</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>10</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Databricks, Tableau, Power BI, Python, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4b965cc65d75bb68</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Data Engineer, Wrapped, Fixed Term</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Spotify</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>10</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, BigQuery, Dataflow, BigQuery, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=328774db5eb1ed52</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Sr. Data Scientist, Clinical</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>10</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Data Scientist, LangChain, RAG, PyTorch, MLflow, Git, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7d05466967329021</t>
         </is>
       </c>
     </row>
